--- a/GroupA.xlsx
+++ b/GroupA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\USTCop\USTCop-Livecast\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB566A16-6E48-4401-A367-38760BBCCED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4036A038-4DF5-4501-BB25-69562C3033A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4260" yWindow="1763" windowWidth="21465" windowHeight="12315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>回合</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -57,6 +57,30 @@
   <si>
     <t>获胜</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HaiT520</t>
+  </si>
+  <si>
+    <t>Re:owp</t>
+  </si>
+  <si>
+    <t>dier4136</t>
+  </si>
+  <si>
+    <t>Witch</t>
+  </si>
+  <si>
+    <t>F.riP</t>
+  </si>
+  <si>
+    <t>Yachie</t>
+  </si>
+  <si>
+    <t>Meph4786</t>
+  </si>
+  <si>
+    <t>ItzBedLA</t>
   </si>
 </sst>
 </file>
@@ -380,7 +404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -417,11 +441,48 @@
       <c r="B2">
         <v>1</v>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>HaiT520</t>
+        </is>
+      </c>
+      <c r="D2">
+        <v>100</v>
+      </c>
+      <c r="E2">
+        <v>100</v>
+      </c>
+      <c r="G2">
+        <v>200</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Re:owp</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>101</v>
+      </c>
+      <c r="E3">
+        <v>99</v>
+      </c>
+      <c r="G3">
+        <v>200</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4">
@@ -430,11 +491,20 @@
       <c r="B4">
         <v>2</v>
       </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>2</v>
       </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6">
@@ -443,11 +513,20 @@
       <c r="B6">
         <v>3</v>
       </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>3</v>
       </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8">
@@ -456,10 +535,19 @@
       <c r="B8">
         <v>4</v>
       </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>4</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">

--- a/GroupA.xlsx
+++ b/GroupA.xlsx
@@ -447,13 +447,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -491,8 +491,22 @@
       <c r="B4">
         <v>2</v>
       </c>
-      <c r="C4" t="s">
-        <v>10</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>dier4136</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
@@ -502,8 +516,22 @@
       <c r="B5">
         <v>6</v>
       </c>
-      <c r="C5" t="s">
-        <v>11</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Witch</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
@@ -513,8 +541,22 @@
       <c r="B6">
         <v>3</v>
       </c>
-      <c r="C6" t="s">
-        <v>12</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>F.riP</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
@@ -524,8 +566,22 @@
       <c r="B7">
         <v>7</v>
       </c>
-      <c r="C7" t="s">
-        <v>13</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Yachie</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
@@ -535,8 +591,22 @@
       <c r="B8">
         <v>4</v>
       </c>
-      <c r="C8" t="s">
-        <v>14</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Meph4786</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
@@ -546,38 +616,178 @@
       <c r="B9">
         <v>8</v>
       </c>
-      <c r="C9" t="s">
-        <v>15</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ItzBedLA</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>5</v>
       </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HaiT520</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>5</v>
       </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Meph4786</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>6</v>
       </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>dier4136</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>6</v>
       </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>F.riP</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>7</v>
       </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>HaiT520</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>7</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>dier4136</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/GroupA.xlsx
+++ b/GroupA.xlsx
@@ -746,21 +746,6 @@
           <t>HaiT520</t>
         </is>
       </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15">
@@ -773,21 +758,6 @@
         <is>
           <t>dier4136</t>
         </is>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
